--- a/Result/profitability/6207.xlsx
+++ b/Result/profitability/6207.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>0.27875</v>
+        <v>0.39125</v>
       </c>
       <c r="N2" t="n">
-        <v>29.835</v>
+        <v>29.79875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34</v>
+        <v>0.4125</v>
       </c>
       <c r="N3" t="n">
-        <v>28.52375</v>
+        <v>28.51375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.29375</v>
+        <v>0.3825</v>
       </c>
       <c r="N4" t="n">
-        <v>26.6825</v>
+        <v>26.11625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2175</v>
+        <v>0.355</v>
       </c>
       <c r="N5" t="n">
-        <v>24.24125</v>
+        <v>24.40375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22625</v>
+        <v>0.3025</v>
       </c>
       <c r="N6" t="n">
-        <v>22.28</v>
+        <v>22.47125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28875</v>
+        <v>0.39375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.54875</v>
+        <v>20.25375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31625</v>
+        <v>0.43875</v>
       </c>
       <c r="N8" t="n">
-        <v>19.20375</v>
+        <v>18.9425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3837499999999999</v>
+        <v>0.38375</v>
       </c>
       <c r="N9" t="n">
         <v>17.78375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6207</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>332</v>
+      </c>
+      <c r="D75" t="n">
+        <v>232</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>74</v>
+      </c>
+      <c r="J75" t="n">
+        <v>89</v>
+      </c>
+      <c r="K75" t="n">
+        <v>85</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.765</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="X75" t="n">
+        <v>16.33333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06523096129837702</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04537521815008727</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
